--- a/experiments/results/resnet34/CIFAR-100/baseline/msp/adaptive/std/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-100/baseline/msp/adaptive/std/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -666,6 +666,55 @@
       <c r="O6" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=None,scale_th=1.5,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>51.03</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>82.56999999999999</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>69.59</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>77.58</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>85.83</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>52.95</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>91.68000000000001</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>76.89</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>78.26000000000001</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>68.48999999999999</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>82.72</v>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=None,scale_th=3.0,type=std</t>
         </is>
       </c>
     </row>
